--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q100_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q100_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001432653515929569</v>
+        <v>0.001387056293735517</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001432653515929569</v>
+        <v>0.001387056293735517</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007009015726453417</v>
+        <v>0.0006864568338165551</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.003849601328827856</v>
+        <v>0.003830738287381522</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003849601328827856</v>
+        <v>0.003830738287381522</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001159236148580563</v>
+        <v>0.001263044484333445</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.007948623834887394</v>
+        <v>0.007866825572686635</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007948623834887394</v>
+        <v>0.007866825572686635</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001963915944597142</v>
+        <v>0.002130423197942778</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01066581008812347</v>
+        <v>0.0105724802526544</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01066581008812347</v>
+        <v>0.0105724802526544</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00268280593340373</v>
+        <v>0.002960685185744275</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01025154083175757</v>
+        <v>0.01014233822524725</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01025154083175757</v>
+        <v>0.01014233822524725</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002588335028036106</v>
+        <v>0.002740483934163141</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.009156948228982022</v>
+        <v>0.009070593802717193</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009156948228982022</v>
+        <v>0.009070593802717193</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002281568301551142</v>
+        <v>0.002433064786614612</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.008187501154120789</v>
+        <v>0.008121903099040685</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008187501154120789</v>
+        <v>0.008121903099040685</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00206631027209007</v>
+        <v>0.002223953738458294</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.007561137631535033</v>
+        <v>0.007507713436646692</v>
       </c>
       <c r="C9" t="n">
-        <v>0.007561137631535033</v>
+        <v>0.007507713436646692</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002006521538362661</v>
+        <v>0.002137796588826696</v>
       </c>
     </row>
   </sheetData>
